--- a/Character.edf_main/Grade.xlsx
+++ b/Character.edf_main/Grade.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bellato</t>
+          <t>Cora</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cora</t>
+          <t>Accretia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Капрал</t>
+          <t>精灵</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Послушник</t>
+          <t>量产型</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -533,12 +533,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Сержант</t>
+          <t>精灵使</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Адепт</t>
+          <t>试作型</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -560,12 +560,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Лейтенант</t>
+          <t>血精灵</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Волхв</t>
+          <t>精锐型</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -587,12 +587,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Капитан</t>
+          <t>大精灵</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Медиум</t>
+          <t>追击型</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,12 +614,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Майор</t>
+          <t>神殿精灵</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Мистик</t>
+          <t>突击型</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -641,12 +641,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Полковник</t>
+          <t>圣光精灵</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Иерарх</t>
+          <t>爆击型</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -668,12 +668,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Генерал</t>
+          <t>神迹精灵</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Жрец</t>
+          <t>强袭型</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -695,12 +695,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Маршал</t>
+          <t>精灵长老</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Избранный</t>
+          <t>星爆型</t>
         </is>
       </c>
       <c r="D10" t="n">
